--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bản v2 — sau rà soát lại bằng Gartner-Lite (Chặng 2) · Đào Ngọc Bích · 2A202601745 · Day 28 Track 01. Cột 'Thay đổi so với v1' ghi rõ từng thay đổi; các thay đổi phát sinh từ kiểm tra chéo Chặng 3 sẽ được bổ sung vào cùng cột này.</t>
+          <t>Bản v2 — sau rà soát chéo nội bộ (Chặng 2) · Nhóm Track1badao · Day 28 Track 01. Phân công từng người: xem bảng thành viên ở README. Cột 'Thay đổi so với v1' ghi rõ từng thay đổi; các thay đổi phát sinh từ kiểm tra chéo Chặng 3 sẽ được bổ sung vào cùng cột này.</t>
         </is>
       </c>
     </row>

--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. AS-IS TO-BE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Lo trinh 30-60-90" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Dashboard chi so" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Thay doi v1 - v2" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +60,20 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +88,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,6 +140,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bản v2 — sau rà soát chéo nội bộ (Chặng 2) · Nhóm Track1badao · Day 28 Track 01. Phân công từng người: xem bảng thành viên ở README. Cột 'Thay đổi so với v1' ghi rõ từng thay đổi; các thay đổi phát sinh từ kiểm tra chéo Chặng 3 sẽ được bổ sung vào cùng cột này.</t>
+          <t>Bản v2 — sau rà soát nội bộ (Chặng 2) và kiểm tra chéo (Chặng 3) · Nhóm Track1badao · Day 28 Track 01. Phân công từng người: xem bảng thành viên ở README. Cột 'Thay đổi so với v1' trên mỗi sheet ghi từng thay đổi; nhật ký đầy đủ ở sheet '6. Thay doi v1 - v2'.</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1943,6 +1966,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1988,7 +2012,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>1. Đo baseline thật cho cả 5 chỉ số.
+          <t>1. Đo baseline thật cho cả 6 chỉ số.
 2. Gán nhãn 100 ca trả lại gần nhất theo loại lỗi (thiếu trường / trích xuất sai / chính sách sai).
 3. Chỉ định Policy Owner cho tập chính sách hoàn tiền.
 4. Dựng bảng phiên bản + ngày hiệu lực cho tập chính sách.</t>
@@ -1996,7 +2020,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>• Bảng baseline có SỐ THẬT cho cả 5 chỉ số (không còn giả định)
+          <t>• Bảng baseline có SỐ THẬT cho cả 6 chỉ số (không còn giả định)
 • Biểu đồ phân bố loại lỗi trên 100 ca
 • Policy Owner có tên trên văn bản phân công
 • 100% văn bản chính sách có phiên bản + ngày hiệu lực</t>
@@ -2100,6 +2124,8 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
@@ -2214,6 +2240,28 @@
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>HÀNG MỚI ở v2 — kill criteria cho chính cơ chế học, thứ v1 chưa có.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Hết giai đoạn 30–60 ngày mà SLA 30 phút cho ca gắn cờ "Không xác định" chưa đạt 95%.</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Cơ chế abstention không vận hành được: AI nói "không biết" nhưng tổ chức không có người tra kịp ⇒ abstention làm chậm khách thay vì bảo vệ khách.</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>KHÔNG mở rộng sang 60–90. Hoặc bố trí người trực hàng đợi cờ đỏ, hoặc tắt abstention và quay lại chuyển người 100% cho nhóm ca này.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>CH4 — HÀNG MỚI ở v2. M5 trước đây có target nhưng không nằm trong điều kiện dừng nào.</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2316,7 +2364,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="105" customHeight="1">
+    <row r="6" ht="115" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>M1</t>
@@ -2374,7 +2422,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="105" customHeight="1">
+    <row r="7" ht="115" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>M2</t>
@@ -2433,7 +2481,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="105" customHeight="1">
+    <row r="8" ht="115" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>M3</t>
@@ -2467,7 +2515,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Log hệ ticket — chênh lệch `ticket_opened_by_agent` → `ticket_approved_first_pass`/`ticket_returned_for_info`; dùng TRUNG VỊ, không dùng trung bình</t>
+          <t>Log hệ ticket — TRUNG VỊ khoảng `ticket_opened_by_agent` → `ticket_approved_first_pass`/`ticket_returned_for_info`; dùng TRUNG VỊ, không dùng trung bình. QUY TẮC ĐO (bổ sung v2): loại khỏi mẫu ca &gt;30 phút và báo cáo riêng tỷ lệ bị loại; ca mở lại nhiều lần chỉ tính lần mở cuối. Lý do: CSKH thường mở ticket rồi để đó làm việc khác — khoảng thời gian thô đo thời gian TRÔI QUA, không đo công sức.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -2487,11 +2535,11 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="105" customHeight="1">
+          <t>CH1 — thêm quy tắc đo: loại ca &gt;30 phút khỏi mẫu và báo cáo riêng tỷ lệ bị loại; ca mở lại nhiều lần chỉ tính lần mở cuối. Lý do: khoảng thời gian thô đo thời gian TRÔI QUA, không đo công sức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="115" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>M4</t>
@@ -2530,12 +2578,12 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Kỹ sư AI</t>
+          <t>Kỹ sư AI (chất lượng trích xuất) · Trưởng nhóm CSKH (đồng duyệt mọi thay đổi ngưỡng cổng chặn)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>&lt;90% ⇒ siết ngưỡng cổng chặn (đẩy thêm trường sang diện 'hỏi lại khách'), ưu tiên sửa nhóm trường sai nhiều nhất trong sprint kế tiếp. &lt;70% ⇒ không mở rộng pilot.</t>
+          <t>&lt;90% ⇒ ưu tiên sửa nhóm trường sai nhiều nhất trong sprint kế tiếp. Siết ngưỡng cổng chặn PHẢI có đồng duyệt của Trưởng nhóm CSKH (bổ sung v2): siết ngưỡng làm khách bị hỏi lại nhiều hơn — đây là quyết định vận hành ảnh hưởng tới khách, không phải quyết định kỹ thuật. &lt;70% ⇒ không mở rộng pilot.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -2545,11 +2593,11 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="105" customHeight="1">
+          <t>CH3 — tách quyền: Kỹ sư AI chịu chất lượng trích xuất, nhưng mọi thay đổi ngưỡng cổng chặn phải có đồng duyệt của Trưởng nhóm CSKH — người quyết không được khác người chịu hậu quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="115" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>M5</t>
@@ -2607,6 +2655,65 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="115" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Chi phí gán nhãn lại ca tra cứu sai mỗi tháng
+(số công × giờ, quy ra tiền)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>5 · Giá trị</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Chưa đo
+(chỉ số mới — v2)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Giảm ≥40% so với baseline tháng đầu</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Bảng công nhóm gán nhãn + số ca vào hàng đợi cải thiện hằng tuần, đối chiếu event `ticket_returned_for_info` đã phân loại lý do "chính sách sai"</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Policy Owner (Vận hành CSKH)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Không giảm sau 2 chu kỳ cập nhật chính sách ⇒ vấn đề nằm ở NGUỒN dữ liệu chứ không ở mô hình: rà lại cấu trúc tập chính sách (tách theo ví, chuẩn hoá điều khoản) trước khi đầu tư thêm vào retrieval. Tăng ⇒ kích hoạt điều kiện DỪNG mở rộng.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Sen có tạo ra tiết kiệm RÒNG hay chỉ dịch chuyển công việc từ CSKH sang nhóm gán nhãn — chỉ số trả lời câu hỏi "có đáng tiền không".</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>CH2 — HÀNG MỚI ở v2. Tầng 5 Giá trị trước đây chỉ có M2, một counter-metric âm. M6 là chỉ số duy nhất trả lời Sen có tạo tiết kiệm RÒNG hay không. Nó lấp đúng lỗ hổng đã nêu khi hạ Direction xuống ĐẠT CÓ ĐIỀU KIỆN: thiếu vế giá trị đặt cạnh chi phí ẩn Day24.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -2614,49 +2721,253 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>1. BASELINE LÀ SỐ GIẢ ĐỊNH. Day23/Day24 là bài phân tích thiết kế, chưa có log vận hành thật. Đo baseline thật là hạng mục số 1 của giai đoạn 0–30 ngày; mọi target ở trên phải được hiệu chỉnh lại sau khi có số thật.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>2. KHÔNG có chỉ số nào ở tầng 1 'Sử dụng' (số login, số câu hỏi, số ticket Sen tạo) — đây là lựa chọn có chủ ý. CSKH bị đẩy việc chứ không tự tìm đến Sen, nên usage luôn ~100% và không nói lên điều gì về việc AI có hữu ích hay không.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>3. M2 có quyền PHỦ QUYẾT M1: không bao giờ được đánh đổi tỷ lệ khiếu nại lại để lấy first-pass. Cặp chỉ số này phải luôn đọc cùng nhau.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>4. Mỗi chỉ số đều có cột 'dẫn tới quyết định gì' — nếu một chỉ số không trả lời được cột này thì phải bỏ khỏi dashboard, vì nó chỉ tạo cảm giác đang đo lường.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>5. v2 KHÔNG thêm chỉ số nào — vẫn đúng 5 chỉ số. Chốt kiểm chất lượng nhãn lý do trả lại ('khác' ≤15%) là điều kiện vận hành của vòng học, đặt ở lộ trình và kill criteria, không đưa lên dashboard: nó không trả lời được cột 'dẫn tới quyết định gì' của một chỉ số sản phẩm.</t>
+          <t>5. (v2) v2 chỉ thêm ĐÚNG MỘT chỉ số — M6 — và thêm được vì nó vượt bài kiểm ở ghi chú 4. Ngược lại, chốt kiểm chất lượng nhãn lý do trả lại ('khác' ≤15%) KHÔNG được đưa lên dashboard vì không vượt được bài kiểm đó; nó nằm ở lộ trình và kill criteria. Đây là cùng một nguyên tắc áp cho hai đề xuất khác nhau, không phải hai quan điểm trái nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>6. (v2) M2 và M6 là hai chỉ số CHẶN, đặt ở hai đầu của cùng một rủi ro: M2 chặn việc mua first-pass bằng chất lượng phục vụ khách; M6 chặn việc mua first-pass bằng công sức của nhóm gán nhãn. Thiếu M6 thì dashboard vẫn có thể 'đẹp' trong khi chi phí chỉ dịch chuyển sang chỗ khác.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A19:K19"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Nhật ký thay đổi sau kiểm tra chéo — v1 → v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Chặng 3 · Người rà soát và tổng hợp: Lương Thanh Trang (2A202601363). ĐIỀN TÊN NHÓM PHẢN BIỆN vào cột "Nguồn góp ý" trước khi nộp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Trục phản biện</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Nguồn góp ý</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Góp ý nhận được</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Thay đổi đã thực hiện ở v2</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Vị trí trong file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm phản biện: ______</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>M3 lấy khoảng cách giữa hai event trong log ticket, nhưng CSKH có thể mở ticket rồi bỏ đó làm việc khác. Số đo được là thời gian TRÔI QUA, không phải công sức — tăng hay giảm đều không đọc được.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Bổ sung quy tắc đo vào cột Nguồn dữ liệu của M3: loại khỏi mẫu ca &gt;30 phút và báo cáo riêng tỷ lệ bị loại; ca mở lại nhiều lần chỉ tính lần mở cuối.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Sheet "5. Dashboard chi so" · M3 · cột Nguồn dữ liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm phản biện: ______</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Tầng 5 (Giá trị) chỉ có M2 — một counter-metric âm. Không chỉ số nào chứng minh Sen tạo ra tiết kiệm RÒNG: first-pass tăng vẫn có thể đi kèm việc chi phí chỉ chuyển từ CSKH sang nhóm gán nhãn.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Thêm M6 — chi phí gán nhãn lại ca tra cứu sai mỗi tháng (tầng 5, product-level), lấy từ khoản chi ẩn đã nêu ở Day24. Owner: Policy Owner. Target giảm ≥40% so với baseline tháng đầu.</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Sheet "5. Dashboard chi so" · dòng M6 (mới) + ghi chú số 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CH3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Hành động</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm phản biện: ______</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>M4 giao owner cho Kỹ sư AI, nhưng hành động khi chỉ số xấu là "siết ngưỡng cổng chặn" — việc này làm khách bị hỏi lại nhiều hơn. Người có quyền quyết định không phải người chịu hậu quả.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Tách quyền ở M4: Kỹ sư AI chịu trách nhiệm chất lượng trích xuất; mọi thay đổi ngưỡng cổng chặn phải có đồng duyệt của Trưởng nhóm CSKH. Ghi rõ lý do trong cột hành động.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Sheet "5. Dashboard chi so" · M4 · cột Owner và Hành động khi chỉ số xấu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Hành động</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm phản biện: ______</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>M5 (SLA 30 phút cho ca gắn cờ) có target nhưng không nằm trong điều kiện dừng nào. Nếu SLA hỏng thì abstention thành cái bẫy làm chậm khách, mà lộ trình vẫn cho phép chuyển giai đoạn.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Thêm một dòng kill criteria: hết giai đoạn 30–60 ngày mà SLA chưa đạt 95% thì không mở rộng — hoặc bố trí người trực hàng đợi cờ đỏ, hoặc tắt abstention và quay lại chuyển người 100% cho nhóm ca này.</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Sheet "4. Lo trinh 30-60-90" · bảng Điều kiện DỪNG</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -122,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,6 +151,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +536,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bản v2 — sau rà soát nội bộ (Chặng 2) và kiểm tra chéo (Chặng 3) · Nhóm Track1badao · Day 28 Track 01. Phân công từng người: xem bảng thành viên ở README. Cột 'Thay đổi so với v1' trên mỗi sheet ghi từng thay đổi; nhật ký đầy đủ ở sheet '6. Thay doi v1 - v2'.</t>
+          <t>Bản v2 — sau rà soát chéo NỘI BỘ trong nhóm (Chặng 2). Kiểm tra chéo với nhóm khác (Chặng 3) CHƯA diễn ra tại thời điểm lập bảng. Nhóm Track1badao · Day 28 Track 01. Phân công từng người: xem bảng thành viên ở README. Cột 'Thay đổi so với v1' trên mỗi sheet ghi từng thay đổi; nhật ký đầy đủ ở sheet '6. Thay doi v1 - v2'.</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1972,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2124,8 +2129,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
@@ -2782,58 +2785,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Nhật ký thay đổi sau kiểm tra chéo — v1 → v2</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nhật ký thay đổi v1 → v2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Chặng 3 · Người rà soát và tổng hợp: Lương Thanh Trang (2A202601363). ĐIỀN TÊN NHÓM PHẢN BIỆN vào cột "Nguồn góp ý" trước khi nộp.</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>NGUỒN: rà soát chéo NỘI BỘ trong nhóm Track1badao — Chặng 3 (kiểm tra chéo với nhóm khác) chưa diễn ra tại thời điểm lập bảng. Khi Chặng 3 diễn ra, bổ sung từ CH9 trở đi và ghi tên nhóm phản biện vào cột 'Người nêu'. Tổng hợp bảng: Lương Thanh Trang (2A202601363).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Trục phản biện</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Nguồn góp ý</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Góp ý nhận được</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Trục rà soát</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Người nêu</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Vấn đề chỉ ra ở v1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Thay đổi đã thực hiện ở v2</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Vị trí trong file</t>
         </is>
@@ -2845,14 +2848,14 @@
           <t>CH1</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Chỉ số</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Nhóm phản biện: ______</t>
+          <t>Lương Thanh Trang · rà soát nội bộ</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2877,14 +2880,14 @@
           <t>CH2</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Chỉ số</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Nhóm phản biện: ______</t>
+          <t>Lương Thanh Trang · rà soát nội bộ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2909,14 +2912,14 @@
           <t>CH3</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Hành động</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Nhóm phản biện: ______</t>
+          <t>Lương Thanh Trang · rà soát nội bộ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2941,14 +2944,14 @@
           <t>CH4</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Hành động</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Nhóm phản biện: ______</t>
+          <t>Lương Thanh Trang · rà soát nội bộ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -2964,6 +2967,134 @@
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Sheet "4. Lo trinh 30-60-90" · bảng Điều kiện DỪNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Chẩn đoán — Gartner-Lite</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Đặng Thái Nam Sơn · rà soát nội bộ</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>v1 chỉ soi Readiness ở nhánh governance. QA mẫu 50 ticket/tuần và hàng đợi ưu tiên SLA 30 phút là CÔNG VIỆC MỚI, chưa giao cho ai và chưa tính vào định biên. Readiness không chỉ là dữ liệu — còn là người và năng lực vận hành thứ mình sắp bật.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Mở Readiness từ 1 lên 4 nhánh, thêm hàng 'Readiness — năng lực vận hành' chấm THIẾU. Gán owner và định biên cho QA mẫu ở bảng kiến trúc tin cậy.</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '2. Chan doan' · bảng 2.2 (hàng mới) · Sheet '3. AS-IS TO-BE' · mắt xích QA mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Chẩn đoán — Gartner-Lite</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Đặng Thái Nam Sơn · rà soát nội bộ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>v1 chấm Direction ĐẠT. Nhưng cả hệ chỉ số chạy trên baseline giả định: target 70% suy ra từ con số 45% không ai đo. Một hướng đi có đích mà chưa có điểm xuất phát đo được thì chưa kiểm chứng được. Thiếu thêm vế giá trị đặt cạnh chi phí ẩn định kỳ đã nêu ở Day24.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Hạ Direction xuống ĐẠT CÓ ĐIỀU KIỆN, ghi rõ cả hai thiếu sót. Vế giá trị sau đó được lấp bằng M6 (CH2) — hai thay đổi này khép cùng một lỗ hổng.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '2. Chan doan' · bảng 2.2 · hàng Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Chẩn đoán — quan hệ nguyên nhân</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Đặng Thái Nam Sơn · rà soát nội bộ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>v1 trình bày NN1 và NN2 như hai việc song song. Nhưng TO-BE đòi mỗi đề xuất hoàn tiền kèm tên văn bản · phiên bản · ngày hiệu lực — không thể trích dẫn phiên bản của một tập dữ liệu chưa có trường phiên bản.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Ghi rõ NN1 và NN2 NỐI TIẾP một nửa: nửa NN1 thuộc hội thoại (trích dẫn đoạn chat, mức tin cậy) làm được ngay; nửa thuộc chính sách bị chặn bởi readiness–dữ liệu của NN2. Phiên bản hoá tập chính sách chuyển thành hạng mục bắt buộc của 0–30 ngày và thành điều kiện Gate.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '2. Chan doan' · kết luận 2.2 và bảng 2.5 · Sheet '4. Lo trinh 30-60-90' · việc chính 0–30 và Gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Cách làm mới — vòng học</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Đặng Thái Nam Sơn · rà soát nội bộ</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>v1 nêu vòng phản hồi nhưng không đặt tên nhịp, hiện vật và người chốt — một vòng lặp không có cuộc họp thì không phải vòng lặp. Dữ liệu học lại do chính CSKH sinh ra đúng lúc họ chịu tải cao nhất; không ràng buộc thì nhãn dồn vào 'khác' và vòng học nhận về nhiễu.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Bốn nhãn lý do trả lại thành lựa chọn BẮT BUỘC, 'khác' phải kèm mô tả. Đặt nhịp: họp rà 30 phút mỗi tuần, hiện vật là bảng phân bố loại lỗi, Policy Owner chốt. Thêm kill criteria: 'khác' &gt;15% sau 2 tuần ⇒ nhãn hỏng. Gate 60–90 đòi phân bố loại lỗi dịch chuyển được so với đường cơ sở 100 ca.</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '3. AS-IS TO-BE' · bước 5 và 7 · Sheet '4. Lo trinh 30-60-90' · kill criteria và dấu hiệu 60–90</t>
         </is>
       </c>
     </row>

--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -540,6 +540,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -614,17 +615,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Tiếp nhận &amp; trích xuất → tạo ticket</t>
+          <t>CSKH tiếp nhận hồ sơ Sen bàn giao và đối chiếu trường trích xuất với lịch sử chat</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Sen hỏi đủ trường bắt buộc, trích xuất mã GD / số tiền / thời gian / tài khoản nhận từ chat tự do.</t>
+          <t>Đầu vào do Sen dựng (hỏi khách, trích mã GD / số tiền / thời gian / tài khoản nhận). Việc của người dùng chính bắt đầu ở bước đối chiếu.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CH11 — viết lại theo góc NGƯỜI DÙNG CHÍNH. v1 mô tả quy trình 1 và 2 bằng hành động của Sen, tức là việc bên trong máy, trong khi persona đã khoá là CSKH. Nội dung không đổi, chủ ngữ đổi.</t>
         </is>
       </c>
     </row>
@@ -636,17 +637,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Tra cứu chính sách hoàn tiền áp dụng</t>
+          <t>CSKH đối chiếu điều khoản chính sách hoàn tiền mà Sen đề xuất</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Sen truy hồi điều khoản chính sách (RAG) để đề xuất hướng xử lý.</t>
+          <t>Sen truy hồi điều khoản (RAG); CSKH kiểm điều khoản có đúng loại sự cố và còn hiệu lực không.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CH11 — viết lại theo góc NGƯỜI DÙNG CHÍNH. v1 mô tả quy trình 1 và 2 bằng hành động của Sen, tức là việc bên trong máy, trong khi persona đã khoá là CSKH. Nội dung không đổi, chủ ngữ đổi.</t>
         </is>
       </c>
     </row>
@@ -658,17 +659,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Thẩm định &amp; duyệt lần đầu của CSKH</t>
+          <t>CSKH thẩm định và quyết định duyệt / trả lại yêu cầu bổ sung</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CSKH mở ticket, xác minh, rồi duyệt hoặc trả lại yêu cầu bổ sung. Trưởng ca duyệt cuối.</t>
+          <t>Trưởng ca duyệt cuối. Sen tuyệt đối không tự duyệt hoàn tiền.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CH11 — viết lại theo góc NGƯỜI DÙNG CHÍNH. v1 mô tả quy trình 1 và 2 bằng hành động của Sen, tức là việc bên trong máy, trong khi persona đã khoá là CSKH. Nội dung không đổi, chủ ngữ đổi.</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1972,6 +1973,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2017,7 +2019,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>1. Đo baseline thật cho cả 6 chỉ số.
+          <t>1. Đo baseline thật cho cả 7 chỉ số.
 2. Gán nhãn 100 ca trả lại gần nhất theo loại lỗi (thiếu trường / trích xuất sai / chính sách sai).
 3. Chỉ định Policy Owner cho tập chính sách hoàn tiền.
 4. Dựng bảng phiên bản + ngày hiệu lực cho tập chính sách.</t>
@@ -2025,7 +2027,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>• Bảng baseline có SỐ THẬT cho cả 6 chỉ số (không còn giả định)
+          <t>• Bảng baseline có SỐ THẬT cho cả 7 chỉ số (không còn giả định)
 • Biểu đồ phân bố loại lỗi trên 100 ca
 • Policy Owner có tên trên văn bản phân công
 • 100% văn bản chính sách có phiên bản + ngày hiệu lực</t>
@@ -2129,6 +2131,8 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
@@ -2265,6 +2269,28 @@
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>CH4 — HÀNG MỚI ở v2. M5 trước đây có target nhưng không nằm trong điều kiện dừng nào.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ khách bị cổng chặn mà không quay lại hoàn tất trong 24 giờ (M7) vượt 15%.</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Cổng chặn đang loại ca khó ra khỏi luồng thay vì bảo vệ chất lượng hồ sơ. Mọi cải thiện của M1 kể từ lúc bật cổng chặn đều không đọc được, vì mẫu ticket đã bị thay đổi.</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>TẮT cổng chặn ngay, quay lại tạo ticket luôn và bù bằng cờ cảnh báo trường thiếu cho CSKH. Đo lại M1 trên mẫu chưa bị lọc trước khi kết luận bất cứ điều gì về first-pass.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>CH9 — HÀNG MỚI ở v2. v1 và v2 trước đây bật cổng chặn mà không viết điều kiện tắt.</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2367,7 +2393,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="115" customHeight="1">
+    <row r="6" ht="118" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>M1</t>
@@ -2425,7 +2451,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="115" customHeight="1">
+    <row r="7" ht="118" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>M2</t>
@@ -2484,7 +2510,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="115" customHeight="1">
+    <row r="8" ht="118" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>M3</t>
@@ -2542,7 +2568,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="115" customHeight="1">
+    <row r="9" ht="118" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>M4</t>
@@ -2600,7 +2626,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="115" customHeight="1">
+    <row r="10" ht="118" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>M5</t>
@@ -2639,12 +2665,13 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Trưởng ca CSKH</t>
+          <t>Trưởng ca CSKH (vận hành hàng đợi)
+· Trưởng nhóm CSKH (đồng chịu trách nhiệm về ĐỊNH BIÊN người trực hàng đợi cờ đỏ)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>&lt;95% ⇒ tăng người trực hàng đợi cờ đỏ. Đây là nhóm ca rủi ro cao nhất; để tồn đọng thì abstention trở thành cái bẫy làm chậm khách thay vì cơ chế an toàn.</t>
+          <t>&lt;95% ⇒ Trưởng ca báo cáo thiếu hụt trong tuần; quyết định tăng định biên thuộc Trưởng nhóm CSKH, KHÔNG thuộc Trưởng ca. Đây là nhóm ca rủi ro cao nhất; để tồn đọng thì abstention trở thành cái bẫy làm chậm khách thay vì cơ chế an toàn.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -2654,11 +2681,11 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="115" customHeight="1">
+          <t>CH12 — tách quyền như đã làm ở M4: nguyên nhân SLA hỏng là định biên, thứ Trưởng ca không tự quyết được. Nhánh readiness 'năng lực vận hành' (CH5) chấm THIẾU chính là chỗ này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="118" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>M6</t>
@@ -2688,7 +2715,8 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Giảm ≥40% so với baseline tháng đầu</t>
+          <t>Đặt SAU khi có baseline (0–30 ngày).
+Ngưỡng tạm coi là có tiến triển: giảm so với tháng liền trước ở 2 chu kỳ liên tiếp.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -2713,66 +2741,135 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>CH2 — HÀNG MỚI ở v2. Tầng 5 Giá trị trước đây chỉ có M2, một counter-metric âm. M6 là chỉ số duy nhất trả lời Sen có tạo tiết kiệm RÒNG hay không. Nó lấp đúng lỗ hổng đã nêu khi hạ Direction xuống ĐẠT CÓ ĐIỀU KIỆN: thiếu vế giá trị đặt cạnh chi phí ẩn Day24.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+          <t>CH2 — HÀNG MỚI ở v2. Tầng 5 Giá trị trước đây chỉ có M2, một counter-metric âm. M6 là chỉ số duy nhất trả lời Sen có tạo tiết kiệm RÒNG hay không. Nó lấp đúng lỗ hổng đã nêu khi hạ Direction xuống ĐẠT CÓ ĐIỀU KIỆN: thiếu vế giá trị đặt cạnh chi phí ẩn Day24.
+CH10 — gỡ target '≥40%': không được đặt mức giảm cụ thể trên một baseline ghi rõ là 'chưa đo'. Đây đúng lỗi đã bắt ở CH6 với Direction, lần này áp cho chính mình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="118" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>% hội thoại bị cổng chặn mà khách KHÔNG quay lại hoàn tất trong 24 giờ
+(COUNTER-METRIC)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>5 · Giá trị</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Chưa đo
+(chỉ số mới — v2)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Đặt SAU khi có baseline (0–30 ngày).
+Ngưỡng chặn cứng: không vượt 10%.</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Log hội thoại — số hội thoại Sen kích hoạt cổng chặn, đối chiếu có ticket được tạo trong 24 giờ hay không; ghép thêm log hotline để bắt ca khách chuyển kênh</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Đào Ngọc Bích (PO)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>&gt;10% ⇒ NỚI cổng chặn: chỉ chặn khi thiếu mã GD, các trường còn lại chuyển sang 'tạo ticket kèm cờ thiếu' thay vì chặn. &gt;15% ⇒ TẮT cổng chặn, quay lại tạo ticket ngay và bù bằng cờ cảnh báo cho CSKH.</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Cổng chặn có được giữ không và siết tới đâu. Đồng thời quyết định M1 có đọc được hay không: M1 tăng trong khi M7 tăng nghĩa là first-pass tăng GIẢ do ca khó đã rụng trước khi thành ticket.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>CH9 — HÀNG MỚI ở v2. Cổng chặn (CH của v1) bắt Sen hỏi lại khách trước khi tạo ticket. Với khách đang mất tiền, hỏi vòng vo dễ khiến họ bỏ sang hotline hoặc bỏ hẳn — ticket không bao giờ được tạo, M1 và M2 đều đẹp lên trong khi khách bị bỏ rơi. v1 và v2 trước đây không có chỉ số nào bắt được rủi ro này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Ghi chú bắt buộc đọc</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>1. BASELINE LÀ SỐ GIẢ ĐỊNH. Day23/Day24 là bài phân tích thiết kế, chưa có log vận hành thật. Đo baseline thật là hạng mục số 1 của giai đoạn 0–30 ngày; mọi target ở trên phải được hiệu chỉnh lại sau khi có số thật.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>2. KHÔNG có chỉ số nào ở tầng 1 'Sử dụng' (số login, số câu hỏi, số ticket Sen tạo) — đây là lựa chọn có chủ ý. CSKH bị đẩy việc chứ không tự tìm đến Sen, nên usage luôn ~100% và không nói lên điều gì về việc AI có hữu ích hay không.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>3. M2 có quyền PHỦ QUYẾT M1: không bao giờ được đánh đổi tỷ lệ khiếu nại lại để lấy first-pass. Cặp chỉ số này phải luôn đọc cùng nhau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>4. Mỗi chỉ số đều có cột 'dẫn tới quyết định gì' — nếu một chỉ số không trả lời được cột này thì phải bỏ khỏi dashboard, vì nó chỉ tạo cảm giác đang đo lường.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
+          <t>3. Mỗi chỉ số đều có cột 'dẫn tới quyết định gì' — nếu một chỉ số không trả lời được cột này thì phải bỏ khỏi dashboard, vì nó chỉ tạo cảm giác đang đo lường.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>5. (v2) v2 chỉ thêm ĐÚNG MỘT chỉ số — M6 — và thêm được vì nó vượt bài kiểm ở ghi chú 4. Ngược lại, chốt kiểm chất lượng nhãn lý do trả lại ('khác' ≤15%) KHÔNG được đưa lên dashboard vì không vượt được bài kiểm đó; nó nằm ở lộ trình và kill criteria. Đây là cùng một nguyên tắc áp cho hai đề xuất khác nhau, không phải hai quan điểm trái nhau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
+          <t>4. (v2) v2 thêm hai chỉ số — M6 và M7 — và cả hai đều vượt được bài kiểm ở ghi chú 3. Ngược lại, chốt kiểm chất lượng nhãn lý do trả lại ('khác' ≤15%) KHÔNG được đưa lên dashboard vì không vượt được bài kiểm đó; nó nằm ở lộ trình và kill criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>6. (v2) M2 và M6 là hai chỉ số CHẶN, đặt ở hai đầu của cùng một rủi ro: M2 chặn việc mua first-pass bằng chất lượng phục vụ khách; M6 chặn việc mua first-pass bằng công sức của nhóm gán nhãn. Thiếu M6 thì dashboard vẫn có thể 'đẹp' trong khi chi phí chỉ dịch chuyển sang chỗ khác.</t>
+          <t>5. (v2) BA CHỈ SỐ CHẶN, đặt ở ba đầu của cùng một rủi ro 'mua first-pass bằng thứ khác'. M2 chặn mua bằng chất lượng phục vụ khách sau khi duyệt · M6 chặn mua bằng công sức của nhóm gán nhãn · M7 chặn mua bằng việc loại ca khó ra khỏi luồng trước khi nó thành ticket. Đọc M1 mà không đọc kèm cả ba là đọc sai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>6. (v2) KHÔNG đặt target dạng phần trăm cụ thể trên một baseline ghi 'chưa đo' (M5, M6, M7). Target của ba chỉ số này chỉ được chốt sau giai đoạn 0–30 ngày. Đặt trước là lặp đúng lỗi đã bắt ở CH6 khi hạ Direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>7. HẠN CHẾ ĐÃ BIẾT: toàn bộ bằng chứng trong bài trích từ tài liệu thiết kế Day23/Day24 của chính nhóm, chưa có quan sát sơ cấp nào (chưa phỏng vấn CSKH thật, chưa xem log thật). Đây là điểm yếu của chẩn đoán, không sửa được bằng viết lại — chỉ sửa được bằng việc đi quan sát ở giai đoạn 0–30 ngày.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A21:K21"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A17:K17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2785,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2806,10 +2903,11 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>NGUỒN: rà soát chéo NỘI BỘ trong nhóm Track1badao — Chặng 3 (kiểm tra chéo với nhóm khác) chưa diễn ra tại thời điểm lập bảng. Khi Chặng 3 diễn ra, bổ sung từ CH9 trở đi và ghi tên nhóm phản biện vào cột 'Người nêu'. Tổng hợp bảng: Lương Thanh Trang (2A202601363).</t>
-        </is>
-      </c>
-    </row>
+          <t>NGUỒN: CH1–CH8 là rà soát chéo NỘI BỘ trong nhóm Track1badao. CH9–CH12 là rà soát đối kháng có hỗ trợ AI trên bản đã gộp. CẢ HAI ĐỀU KHÔNG PHẢI Chặng 3 — kiểm tra chéo với nhóm khác chưa diễn ra tại thời điểm lập bảng; khi có sẽ bổ sung từ CH13 và ghi tên nhóm phản biện vào cột 'Người nêu'. Tổng hợp bảng: Lương Thanh Trang (2A202601363).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3095,6 +3193,134 @@
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Sheet '3. AS-IS TO-BE' · bước 5 và 7 · Sheet '4. Lo trinh 30-60-90' · kill criteria và dấu hiệu 60–90</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="110" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CH9</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Hành động — rủi ro khách hàng</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Rà soát đối kháng có hỗ trợ AI — KHÔNG phải Chặng 3</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Cổng chặn bắt Sen hỏi lại khách trước khi tạo ticket. Với khách đang mất tiền, bị hỏi vòng vo thì họ bỏ sang hotline hoặc bỏ hẳn — ticket không bao giờ được tạo. Hệ quả: số ticket giảm, ca còn lại toàn ca đủ thông tin nên M1 tăng đẹp và M2 cũng không tăng vì khách bỏ đi im lặng. Dashboard xanh trong khi khách bị bỏ rơi. Không chỉ số nào bắt được.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Thêm M7 — % hội thoại bị cổng chặn mà khách không quay lại hoàn tất trong 24 giờ (counter-metric, tầng 5). Thêm một dòng kill criteria: M7 &gt;15% ⇒ tắt cổng chặn. Ghi chú 5 nêu rõ M1 phải đọc kèm cả M2, M6 và M7.</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '5. Dashboard chi so' · dòng M7 (mới) và ghi chú 5 · Sheet '4. Lo trinh 30-60-90' · kill criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CH10</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Chỉ số — kỷ luật đặt target</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Rà soát đối kháng có hỗ trợ AI — KHÔNG phải Chặng 3</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>M6 đặt target 'giảm ≥40% so với baseline tháng đầu' trong khi cột baseline ghi rõ 'chưa đo'. Đây đúng lỗi nhóm vừa bắt ở CH6 khi hạ Direction xuống ĐẠT CÓ ĐIỀU KIỆN — nguyên tắc đã đúng nhưng chưa tự áp lên mình.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Gỡ mọi target phần trăm cụ thể khỏi các chỉ số có baseline 'chưa đo' (M5, M6, M7): target chỉ chốt sau giai đoạn 0–30 ngày. Với M6 giữ một ngưỡng định tính tạm thời. Thêm ghi chú 6 làm nguyên tắc chung.</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '5. Dashboard chi so' · cột Target của M6 (và M7 mới) · ghi chú 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CH11</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Phạm vi — sai chủ ngữ</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Rà soát đối kháng có hỗ trợ AI — KHÔNG phải Chặng 3</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Persona đã khoá là CSKH tuyến 1, nhưng quy trình 1 và 2 được mô tả bằng hành động của Sen (bot hỏi và trích xuất, RAG truy hồi điều khoản) — tức là việc bên trong máy. Chấm nghiêm thì phạm vi chỉ có ĐÚNG MỘT quy trình của người dùng chính, dưới mức 2–4 quy trình mà đề yêu cầu.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Viết lại cả ba quy trình theo góc CSKH: tiếp nhận và đối chiếu trường Sen trích xuất · đối chiếu điều khoản Sen đề xuất · thẩm định và quyết định. Phần việc của Sen chuyển xuống cột Ghi chú làm đầu vào. Nội dung không đổi, chủ ngữ đổi.</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '1. Pham vi' · ba hàng Quy trình 1–3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CH12</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Chỉ số — owner không nắm đòn bẩy</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Rà soát đối kháng có hỗ trợ AI — KHÔNG phải Chặng 3</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Owner của M5 là Trưởng ca CSKH, nhưng nguyên nhân khiến SLA 30 phút hỏng là ĐỊNH BIÊN người trực hàng đợi cờ đỏ — thứ Trưởng ca không tự quyết được, và chính là nhánh readiness 'năng lực vận hành' đã chấm THIẾU ở CH5. Lỗi cùng loại với cái đã sửa ở M4 (CH3) nhưng bị bỏ sót ở M5.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Tách quyền ở M5 như đã làm ở M4: Trưởng ca CSKH vận hành hàng đợi và báo cáo thiếu hụt; Trưởng nhóm CSKH đồng chịu trách nhiệm và là người quyết định tăng định biên.</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Sheet '5. Dashboard chi so' · M5 · cột Owner và Hành động khi chỉ số xấu</t>
         </is>
       </c>
     </row>

--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -540,7 +540,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1972,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2131,8 +2129,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
@@ -2335,6 +2331,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -2806,6 +2804,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -2851,7 +2850,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>6. (v2) KHÔNG đặt target dạng phần trăm cụ thể trên một baseline ghi 'chưa đo' (M5, M6, M7). Target của ba chỉ số này chỉ được chốt sau giai đoạn 0–30 ngày. Đặt trước là lặp đúng lỗi đã bắt ở CH6 khi hạ Direction.</t>
+          <t>6. (v2) KHÔNG đặt target dạng phần trăm cụ thể trên một baseline ghi 'chưa đo' — áp cho M6 và M7; target của hai chỉ số này chỉ chốt sau giai đoạn 0–30 ngày. Đặt trước là lặp đúng lỗi đã bắt ở CH6 khi hạ Direction. M5 là ngoại lệ có lý do: 95% là một CAM KẾT SLA do tổ chức tự đặt ra, không phải mức cải thiện suy ra từ hiện trạng — loại target này không cần baseline mới đặt được.</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2906,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
